--- a/docs/assets/templates/sighting_import.xlsx
+++ b/docs/assets/templates/sighting_import.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anastasia/Desktop/New Bulk Import spreadsheet templates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anastasia/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB21D5E9-99F3-FD40-BED9-8723497D20D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B8024BA-D838-2B43-84EC-B9CE269E2781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17080" xr2:uid="{A263B153-333A-4242-B05A-7E4C4091D521}"/>
   </bookViews>
@@ -84,19 +84,19 @@
     <t>Sighting.individualCount</t>
   </si>
   <si>
-    <t>Sighting.year</t>
-  </si>
-  <si>
-    <t>Sighting.month</t>
-  </si>
-  <si>
-    <t>Sighting.day</t>
-  </si>
-  <si>
-    <t>Sighting.hour</t>
-  </si>
-  <si>
-    <t>Sighting.minutes</t>
+    <t>Encounter.year</t>
+  </si>
+  <si>
+    <t>Encounter.month</t>
+  </si>
+  <si>
+    <t>Encounter.day</t>
+  </si>
+  <si>
+    <t>Encounter.hour</t>
+  </si>
+  <si>
+    <t>Encounter.minutes</t>
   </si>
 </sst>
 </file>
@@ -495,11 +495,11 @@
     <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="19.1640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="22.5" bestFit="1" customWidth="1"/>
